--- a/files/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/files/SWDY_Valuation_Model_05082026_public.xlsx
@@ -36,8 +36,8 @@
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00x"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.00x"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
   <fonts count="11">
@@ -143,6 +143,7 @@
     <xf numFmtId="164" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,13 +154,12 @@
     <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -619,73 +619,77 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>THREE THINGS ARE PASTED VALUES, and it is worth knowing which. First, audited and disclosed history — the</t>
+          <t>THREE THINGS ARE PASTED VALUES, and it is worth knowing exactly which. First, audited and disclosed history</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>primary record, not a calculation. Second, the sub-segment unit build: revenue and gross profit per segment</t>
+          <t>— the primary record, not a calculation. Second, the segment build: revenue and profit for the three</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>come from a seven-line tonnage, megavolt-ampere, meter-unit and order-book model, and only its OUTPUT is</t>
+          <t>segments the company itself discloses (Cables and its accessories, Constructions and infrastructure,</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>carried here; everything downstream of it is formula. Third, the Monte Carlo price map and the sensitivity</t>
+          <t>Electrical products and digital solutions) are pasted for FY2025 and grown on their own drivers; only its</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>grids, where each individual cell is a complete re-run of the whole valuation and so cannot be a formula in</t>
+          <t>OUTPUT is carried here and everything downstream of it is formula. Third, whole-model engine outputs, where</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>a grid. Changing a driver reprices the model but does NOT redraw those two grids.</t>
+          <t>each figure is a complete re-run of the entire valuation and so cannot be a single formula: the Monte Carlo</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>price map, the sensitivity grids, the DCF scenario bear/bull bounds, the multi-leg currency-of-discounting</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>How revenue is built. Not as one growth rate. Revenue splits into a domestic Egyptian-pound leg and a</t>
+          <t>alternative (its USD cost of capital IS a live formula; the leg-by-leg USD discounting is the engine's),</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>foreign leg forecast in US dollars and translated at an explicit exchange-rate path, because more than 70%</t>
+          <t>and the expert-panel legs. Everything else — including every lens base value, the relative/normalised/book</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>of this company's revenue is earned outside Egypt. Margins come from a segment build; group EBITDA margin</t>
+          <t>bear and bull bounds, and the anchor-date roll — is a live formula. Changing a driver reprices the model</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>is an output of that build, not an input.</t>
+          <t>but does NOT redraw the engine outputs.</t>
         </is>
       </c>
     </row>
@@ -695,135 +699,135 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
+          <t>How revenue is built. Not as one growth rate. Each of the three disclosed segments is grown on its own</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>shown as ranges.</t>
+          <t>driver — Cables on copper-price growth times FX-translation growth times a modest real-volume assumption,</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Constructions and Electrical products on a taper of their own recent revenue CAGR — because none of the</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Sourcing note, up front. FY2023 and FY2024 come from the company's audited consolidated statements and</t>
+          <t>audited filings discloses a tonnage, order-book or backlog figure to build a literal unit model from.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>earnings releases and are not estimated. For FY2025, revenue, profit after tax, profit after minority</t>
+          <t>Margins come from the same segment build; group EBITDA margin is an OUTPUT of it, not an input.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>interests, total assets and net bank debt are disclosed; the intermediate income-statement lines are</t>
-        </is>
-      </c>
+      <c r="A30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>derived by closing the profit-and-loss account to the reported profit, and the balance sheet beyond total</t>
+          <t>What it is not. It is not investment advice, a recommendation, or a price target. Values are model outputs</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>assets and net debt is triangulated by three methods, which are shown and averaged on the Balance Sheet</t>
+          <t>shown as ranges.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>sheet rather than asserted. Every derived line is annotated where it appears and listed with source and</t>
-        </is>
-      </c>
+      <c r="A33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>date in the companion bibliography document.</t>
+          <t>Sourcing note, up front. FY2023, FY2024 and FY2025 all come from the company's own audited consolidated</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>financial statements — every income-statement, balance-sheet and segment line is the audited figure, not a</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
+          <t>derivation or a triangulation. Segment revenue ties EXACTLY to consolidated revenue in every year (Note</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26.9% -&gt; 15.1% on the same easing calendar as the interest forecast; the terminal value is</t>
+          <t>5-3); segment profit reconciles to consolidated operating profit through an explicit, exactly-reconciling</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
+          <t>corporate cost load (Note 16 less G&amp;A, net impairment, other expenses and other income). Every input is</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>The glide fractions are not a free parameter: they are the cost-of-debt path's own cumulative progress, and</t>
+          <t>annotated where it appears and listed with source and date in the companion bibliography document.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>the DCF sheet computes them in front of you.</t>
-        </is>
-      </c>
+      <c r="A40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Discount convention. Each explicit year is discounted at its own forward cost of capital, gliding</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>The open question. This company earns most of its revenue in hard currency but reports, lists and borrows</t>
+          <t>26.6% -&gt; 15.9% on the same easing calendar as the interest forecast; the terminal value is</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>in Egyptian pounds. The primary model charges the full Egyptian cost of capital. The Fundamental Valuation</t>
+          <t>capitalised at the terminal rate and discounted at the year-5 cumulative factor. One date, one price of time.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>sheet also shows what the same cash flows are worth if the hard-currency leg is discounted at a</t>
+          <t>The glide fractions are not a free parameter: they are the cost-of-debt path's own cumulative progress, and</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>hard-currency rate. Both are shown; they are not averaged.</t>
+          <t>the DCF sheet computes them in front of you.</t>
         </is>
       </c>
     </row>
@@ -833,26 +837,57 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+          <t>The open question. This company earns just over half its revenue on a hard-currency-linked basis but</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+          <t>reports, lists and borrows in Egyptian pounds. The primary model charges the full Egyptian cost of capital.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+          <t>The Fundamental Valuation sheet also shows what the same cash flows are worth if the hard-currency leg is</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>discounted at a hard-currency rate. Both are shown; they are not averaged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Currency. EGP million unless stated. Spot EGP 105.20 (2026-08-05 close). Sheets: READ FIRST · Summary ·</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Fundamental Valuation · Assumptions · SOTP Bridge · Segments · Relative &amp; Normalized · DCF · Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Statement · Balance Sheet · Cash Flow · Summary Financials · Monte Carlo · Sensitivity · Per-Share &amp;</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Ratios · Peer &amp; Sector.</t>
         </is>
@@ -869,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -901,7 +936,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>EGP mn, consolidated. The FY2025 debt and cash lines are triangulated by three methods, shown and averaged below rather than asserted</t>
+          <t>EGP mn, consolidated. Every FY2023-25 line is the audited closing figure — no triangulation is needed for any year, including FY2025, because the full filing is in hand</t>
         </is>
       </c>
     </row>
@@ -958,33 +993,32 @@
           <t>Property, plant and equipment</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
-        <v>18009.2</v>
-      </c>
-      <c r="C5" s="22" t="n">
-        <v>27543.8</v>
-      </c>
-      <c r="D5" s="28">
-        <f>C5+'Income Statement'!D5*(Assumptions!$B$33-Assumptions!$C$34)</f>
-        <v/>
-      </c>
-      <c r="E5" s="28">
+      <c r="B5" s="23" t="n">
+        <v>18009.166367</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>27543.762675</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>35961.076614</v>
+      </c>
+      <c r="E5" s="29">
         <f>D5-DCF!B12+DCF!B8</f>
         <v/>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <f>E5-DCF!C12+DCF!C8</f>
         <v/>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="29">
         <f>F5-DCF!D12+DCF!D8</f>
         <v/>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="29">
         <f>G5-DCF!E12+DCF!E8</f>
         <v/>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="29">
         <f>H5-DCF!F12+DCF!F8</f>
         <v/>
       </c>
@@ -995,16 +1029,14 @@
           <t>Inventories</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
-        <v>30881.8</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>56795.9</v>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="23" t="n">
+        <v>30881.822082</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>56795.884068</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>59860.04457</v>
       </c>
     </row>
     <row r="7">
@@ -1013,16 +1045,14 @@
           <t>Contract assets</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
-        <v>16179.6</v>
-      </c>
-      <c r="C7" s="22" t="n">
-        <v>18052</v>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="23" t="n">
+        <v>16179.633722</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>18051.96657</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>29894.579591</v>
       </c>
     </row>
     <row r="8">
@@ -1031,16 +1061,14 @@
           <t>Trade and other receivables</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n">
-        <v>46591.9</v>
-      </c>
-      <c r="C8" s="22" t="n">
-        <v>86736.3</v>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="23" t="n">
+        <v>46591.885092</v>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>86736.309423</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>116259.797169</v>
       </c>
     </row>
     <row r="9">
@@ -1049,13 +1077,13 @@
           <t>Cash and cash equivalents</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
-        <v>25552</v>
-      </c>
-      <c r="C9" s="22" t="n">
-        <v>38180</v>
-      </c>
-      <c r="D9" s="28">
+      <c r="B9" s="23" t="n">
+        <v>25552.0448</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>38180.002322</v>
+      </c>
+      <c r="D9" s="29">
         <f>D11-D17</f>
         <v/>
       </c>
@@ -1066,14 +1094,14 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="B10" s="29" t="n">
-        <v>151448.7</v>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>249527.1</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>311090</v>
+      <c r="B10" s="30" t="n">
+        <v>151448.654828</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>249527.138687</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>311099.090775</v>
       </c>
       <c r="E10" s="15" t="n"/>
       <c r="F10" s="15" t="n"/>
@@ -1087,15 +1115,14 @@
           <t>Loans and borrowings</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
-        <v>41766.5</v>
-      </c>
-      <c r="C11" s="22" t="n">
-        <v>59082.9</v>
-      </c>
-      <c r="D11" s="28">
-        <f>AVERAGE(B23:B25)</f>
-        <v/>
+      <c r="B11" s="23" t="n">
+        <v>41766.492071</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>59082.941807</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>62509.211797</v>
       </c>
     </row>
     <row r="12">
@@ -1104,16 +1131,14 @@
           <t>Trade and other payables</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
-        <v>31938.1</v>
-      </c>
-      <c r="C12" s="22" t="n">
-        <v>54808.2</v>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="23" t="n">
+        <v>31938.12206</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>54808.185042</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>68895.662044</v>
       </c>
     </row>
     <row r="13">
@@ -1122,16 +1147,14 @@
           <t>Contract liabilities</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
-        <v>25060.3</v>
-      </c>
-      <c r="C13" s="22" t="n">
-        <v>53281.1</v>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="23" t="n">
+        <v>25060.328092</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>53281.056753</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>81266.224686</v>
       </c>
     </row>
     <row r="14">
@@ -1140,34 +1163,33 @@
           <t>Equity attributable to shareholders</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>35724.5</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>55274.9</v>
-      </c>
-      <c r="D14" s="29">
-        <f>C14+'Income Statement'!D17-Assumptions!$C$55*Assumptions!$C$6</f>
-        <v/>
-      </c>
-      <c r="E14" s="29">
-        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$56)</f>
-        <v/>
-      </c>
-      <c r="F14" s="29">
-        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$56)</f>
-        <v/>
-      </c>
-      <c r="G14" s="29">
-        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$56)</f>
-        <v/>
-      </c>
-      <c r="H14" s="29">
-        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$56)</f>
-        <v/>
-      </c>
-      <c r="I14" s="29">
-        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$56)</f>
+      <c r="B14" s="30" t="n">
+        <v>35724.466132</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>55274.913356</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>66870.86655000001</v>
+      </c>
+      <c r="E14" s="30">
+        <f>D14+'Income Statement'!E17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="F14" s="30">
+        <f>E14+'Income Statement'!F17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="G14" s="30">
+        <f>F14+'Income Statement'!G17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="H14" s="30">
+        <f>G14+'Income Statement'!H17*(1-Assumptions!$C$50)</f>
+        <v/>
+      </c>
+      <c r="I14" s="30">
+        <f>H14+'Income Statement'!I17*(1-Assumptions!$C$50)</f>
         <v/>
       </c>
     </row>
@@ -1177,14 +1199,14 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
-        <v>2384</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>4251.8</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>5851.8</v>
+      <c r="B15" s="23" t="n">
+        <v>2384.013396</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>4251.7719</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>5118.978381</v>
       </c>
     </row>
     <row r="16">
@@ -1193,34 +1215,33 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
-        <v>36654.90000000001</v>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>53494.90000000002</v>
-      </c>
-      <c r="D16" s="28">
-        <f>'Income Statement'!D5*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="E16" s="28">
-        <f>'Income Statement'!E5*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="F16" s="28">
-        <f>'Income Statement'!F5*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="G16" s="28">
-        <f>'Income Statement'!G5*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="H16" s="28">
-        <f>'Income Statement'!H5*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="I16" s="28">
-        <f>'Income Statement'!I5*Assumptions!$C$32</f>
+      <c r="B16" s="23" t="n">
+        <v>36654.89074399999</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>53494.91826600001</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>55852.53459999998</v>
+      </c>
+      <c r="E16" s="29">
+        <f>'Income Statement'!E5*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="F16" s="29">
+        <f>'Income Statement'!F5*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="G16" s="29">
+        <f>'Income Statement'!G5*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="H16" s="29">
+        <f>'Income Statement'!H5*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="I16" s="29">
+        <f>'Income Statement'!I5*Assumptions!$C$25</f>
         <v/>
       </c>
     </row>
@@ -1230,34 +1251,34 @@
           <t>Net bank debt</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>14768</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>20028</v>
-      </c>
-      <c r="D17" s="29">
-        <f>Assumptions!$C$50</f>
-        <v/>
-      </c>
-      <c r="E17" s="29">
-        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!E17</f>
-        <v/>
-      </c>
-      <c r="F17" s="29">
-        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!F17</f>
-        <v/>
-      </c>
-      <c r="G17" s="29">
-        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!G17</f>
-        <v/>
-      </c>
-      <c r="H17" s="29">
-        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!H17</f>
-        <v/>
-      </c>
-      <c r="I17" s="29">
-        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$56*'Income Statement'!I17</f>
+      <c r="B17" s="30" t="n">
+        <v>16214.447271</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>20902.939485</v>
+      </c>
+      <c r="D17" s="30">
+        <f>Assumptions!$C$43</f>
+        <v/>
+      </c>
+      <c r="E17" s="30">
+        <f>D17-DCF!B14-'Income Statement'!E11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!E17</f>
+        <v/>
+      </c>
+      <c r="F17" s="30">
+        <f>E17-DCF!C14-'Income Statement'!F11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!F17</f>
+        <v/>
+      </c>
+      <c r="G17" s="30">
+        <f>F17-DCF!D14-'Income Statement'!G11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!G17</f>
+        <v/>
+      </c>
+      <c r="H17" s="30">
+        <f>G17-DCF!E14-'Income Statement'!H11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!H17</f>
+        <v/>
+      </c>
+      <c r="I17" s="30">
+        <f>H17-DCF!F14-'Income Statement'!I11*(1-Assumptions!$C$7)+Assumptions!$C$50*'Income Statement'!I17</f>
         <v/>
       </c>
     </row>
@@ -1267,35 +1288,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="35">
         <f>B17/'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="35">
         <f>C17/'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D18" s="34">
+      <c r="D18" s="35">
         <f>D17/'Income Statement'!D7</f>
         <v/>
       </c>
-      <c r="E18" s="34">
+      <c r="E18" s="35">
         <f>E17/'Income Statement'!E7</f>
         <v/>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="35">
         <f>F17/'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="35">
         <f>G17/'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="35">
         <f>H17/'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="I18" s="34">
+      <c r="I18" s="35">
         <f>I17/'Income Statement'!I7</f>
         <v/>
       </c>
@@ -1306,78 +1327,24 @@
           <t>Residual: other liabilities, provisions and deferred tax not shown separately (total assets less the lines above)</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="29">
         <f>B10-(B11+B12+B13+B14+B15)</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="29">
         <f>C10-(C11+C12+C13+C14+C15)</f>
         <v/>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="D19" s="29">
+        <f>D10-(D11+D12+D13+D14+D15)</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Note: this is a CONDENSED layout, so it does not foot to zero — the residual row above is the block of other liabilities, provisions, deferred tax and related-party balances that is not shown separately. For FY2024 that residual is 22,828, which reconciles to the audited statements (provisions 13,440 + 943, deferred tax 3,670, related parties 2,050 + 95, other liabilities 2,631 = 22,829). FY2025 shows only the disclosed lines (total assets, net bank debt) plus rolled-forward equity and triangulated debt and cash; the valuation bridge uses only the disclosed net bank debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>FY2025 gross debt — three independent triangulations</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>EGP mn</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Balance-sheet residual (assets less equity and non-debt liabilities)</t>
-        </is>
-      </c>
-      <c r="B23" s="22" t="n">
-        <v>76165.80577232633</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>FY2024 debt scaled with revenue growth</t>
-        </is>
-      </c>
-      <c r="B24" s="22" t="n">
-        <v>71579.70996905792</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Implied from the cash balance and the disclosed net debt</t>
-        </is>
-      </c>
-      <c r="B25" s="22" t="n">
-        <v>67104.64586101151</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Average — the figure carried on row 11</t>
-        </is>
-      </c>
-      <c r="B26" s="29">
-        <f>AVERAGE(B23:B25)</f>
-        <v/>
+          <t>Note: this is a CONDENSED layout, so it does not foot to zero — the residual row above is the block of other liabilities, provisions, deferred tax and related-party balances that is not shown separately. For FY2024 that residual is 22,828, which reconciles to the audited statements (provisions 13,440 + 943, deferred tax 3,670, related parties 2,050 + 95, other liabilities 2,631 = 22,829). Every line, including FY2025, is now the audited closing figure — no triangulation or roll-forward is used for any historical year.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1435,12 +1402,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1476,11 +1443,11 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>'Income Statement'!B7</f>
+        <f>'Income Statement'!C7</f>
         <v/>
       </c>
       <c r="C5" s="18">
-        <f>'Income Statement'!C7</f>
+        <f>'Income Statement'!D7</f>
         <v/>
       </c>
       <c r="D5" s="18">
@@ -1510,13 +1477,13 @@
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
-        <v>-7706.9</v>
+      <c r="C6" s="23" t="n">
+        <v>-5740.31242</v>
       </c>
     </row>
     <row r="7">
@@ -1525,13 +1492,13 @@
           <t>Income tax paid</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
-        <v>-4891</v>
+      <c r="C7" s="23" t="n">
+        <v>-8298.752112</v>
       </c>
     </row>
     <row r="8">
@@ -1540,13 +1507,13 @@
           <t>Operating cash flow after interest and tax</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
-        <v>3979.4</v>
+      <c r="C8" s="23" t="n">
+        <v>12765.922545</v>
       </c>
     </row>
     <row r="9">
@@ -1555,12 +1522,12 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1592,12 +1559,12 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1629,11 +1596,11 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
-        <v>-4830</v>
-      </c>
-      <c r="C11" s="22" t="n">
-        <v>-8765.700000000001</v>
+      <c r="B11" s="23" t="n">
+        <v>-8489.780912</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>-13112.049791</v>
       </c>
       <c r="D11" s="18">
         <f>DCF!B12</f>
@@ -1662,13 +1629,13 @@
           <t>Change in working capital</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="28">
-        <f>-('Balance Sheet'!C16-'Balance Sheet'!B16)</f>
+      <c r="C12" s="29">
+        <f>-('Balance Sheet'!D16-'Balance Sheet'!C16)</f>
         <v/>
       </c>
       <c r="D12" s="18">
@@ -1698,33 +1665,33 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>D9+D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>E9+E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>F9+F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>G9+G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="30">
         <f>H9+H10+H11+H12</f>
         <v/>
       </c>
@@ -1733,7 +1700,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Cash conversion — operating cash flow as a share of EBITDA, FY2024</t>
+          <t>Cash conversion — operating cash flow as a share of EBITDA, FY2025</t>
         </is>
       </c>
       <c r="C15" s="11">
@@ -2083,17 +2050,17 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D11" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2164,38 +2131,38 @@
           <t>Invested capital</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="D13" s="18">
-        <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!D16+'Balance Sheet'!D5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="E13" s="18">
-        <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!E16+'Balance Sheet'!E5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="F13" s="18">
-        <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!F16+'Balance Sheet'!F5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="G13" s="18">
-        <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!G16+'Balance Sheet'!G5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!H16+'Balance Sheet'!H5+Assumptions!$C$45</f>
         <v/>
       </c>
       <c r="I13" s="18">
-        <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$52</f>
+        <f>'Balance Sheet'!I16+'Balance Sheet'!I5+Assumptions!$C$45</f>
         <v/>
       </c>
     </row>
@@ -2467,7 +2434,7 @@
           <t>Simulated paths</t>
         </is>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <v>50000</v>
       </c>
     </row>
@@ -2515,10 +2482,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -2587,111 +2554,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>71.48013737611937</v>
+        <v>65.329844401984</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>75.158505958635</v>
+        <v>68.35354257523431</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>79.66249997898875</v>
+        <v>71.9670712933261</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>85.33897230281774</v>
+        <v>76.39345107557055</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>92.76070177891306</v>
+        <v>81.98435185876774</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>64.51999723358476</v>
+        <v>58.4402879098668</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>67.23266415979741</v>
+        <v>60.6461755538821</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>70.47099233404454</v>
+        <v>63.21971152566643</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>74.42869060586594</v>
+        <v>66.28434770102153</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>79.40797299188714</v>
+        <v>70.02577372147603</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>58.71390500851878</v>
+        <v>52.6302713847032</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>60.7356474116613</v>
+        <v>54.24351203947743</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>65.90739638220869</v>
+        <v>58.22034038779206</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>69.3345836803008</v>
+        <v>60.75189974055389</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>53.79809034203993</v>
+        <v>47.66687793345727</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>55.314134925563</v>
+        <v>48.84248007666995</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>57.04924305755583</v>
+        <v>50.15437928765454</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>59.06822004769293</v>
+        <v>51.63997115359249</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>61.46422928886715</v>
+        <v>53.35170855849378</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>49.58340787307901</v>
+        <v>43.37959572111903</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>50.72236517614795</v>
+        <v>44.22702715685592</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>52.00135637265844</v>
+        <v>45.15076181775254</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>53.45808918007977</v>
+        <v>46.16998066974453</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>55.14514468831749</v>
+        <v>47.31088154269673</v>
       </c>
     </row>
     <row r="12">
@@ -2705,171 +2672,160 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>terminal 13.1%</t>
+          <t>terminal 13.9%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>84.33728753089692</v>
+        <v>76.53066395732843</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>81.95820408756369</v>
+        <v>74.20763706152702</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>79.66249997898875</v>
+        <v>71.9670712933261</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>77.44651129819714</v>
+        <v>69.80531513594863</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>75.30676865150218</v>
+        <v>67.71891197265076</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>terminal 14.1%</t>
+          <t>terminal 14.9%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>74.62341007610547</v>
+        <v>67.28261009519261</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>72.51027129509237</v>
+        <v>65.21451934442834</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>70.47099233404454</v>
+        <v>63.21971152566643</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>68.50233381059978</v>
+        <v>61.29494639096928</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>66.60122807292484</v>
+        <v>59.4371564326104</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>terminal 15.1%</t>
+          <t>terminal 15.9%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>66.82989265057586</v>
+        <v>59.73868410008669</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>64.9300279088521</v>
+        <v>57.87843695583718</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>61.32608564835102</v>
+        <v>54.35244928326305</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>59.61636320712214</v>
+        <v>52.68105291114693</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>terminal 16.1%</t>
+          <t>terminal 16.9%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>60.43940513969982</v>
+        <v>53.47006721636905</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>58.71433541623137</v>
+        <v>51.78242507173835</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>57.04924305755583</v>
+        <v>50.15437928765454</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>55.44150743399135</v>
+        <v>48.58330249404308</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>53.88864645585161</v>
+        <v>47.06670705720629</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>terminal 17.1%</t>
+          <t>terminal 17.9%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>55.10506833536628</v>
+        <v>48.18057399728519</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>53.52583022982751</v>
+        <v>46.63848559892643</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>52.00135637265844</v>
+        <v>45.15076181775254</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>50.52925833918371</v>
+        <v>43.71500938002328</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>49.1072737958847</v>
+        <v>42.32896215043171</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Single-driver sensitivities</t>
+          <t>Single-driver sensitivities — five engine re-runs per row; the parameter grid for each row is shown beside its name</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+          <t>Driver (parameter grid)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="inlineStr"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Swing</t>
         </is>
@@ -2878,23 +2834,23 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Beta  (0.60 / 0.80 / 1.01 / 1.15 / 1.30)</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>86.86398352810841</v>
+        <v>82.1040695099194</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>73.76938856958702</v>
+        <v>67.65449935590391</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>57.1692154119707</v>
+        <v>49.74342393917833</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>51.73397898456535</v>
+        <v>43.98578978959206</v>
       </c>
       <c r="H22" s="10">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2904,23 +2860,23 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Exchange-rate path multiplier</t>
+          <t>Exchange-rate path multiplier  (0.90x / 1.00x / 1.20x / 1.45x / 1.70x)</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>71.93944315776433</v>
+        <v>52.41845656686412</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>45.41028961005051</v>
+        <v>63.41506818792391</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>23.30266165362228</v>
+        <v>72.57891120547374</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1.195033697194072</v>
+        <v>81.74275422302357</v>
       </c>
       <c r="H23" s="10">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2930,23 +2886,23 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>EBITDA margin shift</t>
+          <t>Segment margins, multiplicative  (0.850x / 0.925x / 1.000x / 1.075x / 1.150x)</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>42.21530497281732</v>
+        <v>30.09596871603819</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>52.6558484740052</v>
+        <v>43.08998124496109</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>73.53693547638095</v>
+        <v>69.078006302807</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>83.97747897756886</v>
+        <v>82.07201883172988</v>
       </c>
       <c r="H24" s="10">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2956,23 +2912,23 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue</t>
+          <t>Copper price multiplier  (0.850x / 0.925x / 1.000x / 1.075x / 1.150x)</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>66.1820174425543</v>
+        <v>50.58568796335414</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>64.63920470887369</v>
+        <v>53.33484086861908</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>61.55357924151245</v>
+        <v>58.83314667914899</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>60.01076650783185</v>
+        <v>61.58229958441391</v>
       </c>
       <c r="H25" s="10">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2982,26 +2938,78 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
+          <t>Working capital / revenue  (17.0% / 18.5% / 19.9% / 21.5% / 23.0%)</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>55.97972245871841</v>
+        <v>62.98785448545478</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>59.77877118391308</v>
+        <v>59.41689204843545</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>63.09639197519306</v>
+        <v>56.08399377388404</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>65.62346153036643</v>
+        <v>52.27496717439674</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>67.37686863430243</v>
+        <v>48.70400473737737</v>
       </c>
       <c r="H26" s="10">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Terminal return on invested capital  (15.0% / 18.0% / 20.4% / 26.0% / 30.0%)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>49.68012825683863</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>53.7154504510227</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>56.08399377388404</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>59.92363844207513</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>61.78609483939085</v>
+      </c>
+      <c r="H27" s="10">
+        <f>MAX(B27:F27)-MIN(B27:F27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth (at base cost of capital)  (3% / 4% / 5% / 6% / 7%)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>52.6302713847032</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>54.24351203947743</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>56.08399377388404</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>58.22034038779206</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>60.75189974055389</v>
+      </c>
+      <c r="H28" s="10">
+        <f>MAX(B28:F28)-MIN(B28:F28)</f>
         <v/>
       </c>
     </row>
@@ -3463,35 +3471,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="35">
         <f>'Balance Sheet'!B18</f>
         <v/>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="35">
         <f>'Balance Sheet'!C18</f>
         <v/>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="35">
         <f>'Balance Sheet'!D18</f>
         <v/>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="35">
         <f>'Balance Sheet'!E18</f>
         <v/>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="35">
         <f>'Balance Sheet'!F18</f>
         <v/>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="35">
         <f>'Balance Sheet'!G18</f>
         <v/>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="35">
         <f>'Balance Sheet'!H18</f>
         <v/>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="35">
         <f>'Balance Sheet'!I18</f>
         <v/>
       </c>
@@ -3502,36 +3510,36 @@
           <t>Interest cover (EBIT / net interest)</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>-'Income Statement'!C10/'Income Statement'!C11</f>
         <v/>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>-'Income Statement'!D10/'Income Statement'!D11</f>
         <v/>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>-'Income Statement'!E10/'Income Statement'!E11</f>
         <v/>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>-'Income Statement'!F10/'Income Statement'!F11</f>
         <v/>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="35">
         <f>-'Income Statement'!G10/'Income Statement'!G11</f>
         <v/>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="35">
         <f>-'Income Statement'!H10/'Income Statement'!H11</f>
         <v/>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="35">
         <f>-'Income Statement'!I10/'Income Statement'!I11</f>
         <v/>
       </c>
@@ -3581,18 +3589,18 @@
           <t>Capital expenditure / revenue</t>
         </is>
       </c>
-      <c r="B17" s="11">
-        <f>-'Cash Flow'!B11/'Income Statement'!B5</f>
-        <v/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C17" s="11">
-        <f>-'Cash Flow'!C11/'Income Statement'!C5</f>
-        <v/>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <f>-'Cash Flow'!B11/'Income Statement'!C5</f>
+        <v/>
+      </c>
+      <c r="D17" s="11">
+        <f>-'Cash Flow'!C11/'Income Statement'!D5</f>
+        <v/>
       </c>
       <c r="E17" s="11">
         <f>-'Cash Flow'!D11/'Income Statement'!E5</f>
@@ -3622,13 +3630,13 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.2079305448304614</v>
+        <v>0.2012516504606288</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.3172037113507076</v>
+        <v>0.3037580263923543</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.2640762760437433</v>
+        <v>0.5146285136141233</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
@@ -3663,13 +3671,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>0.04635583499957009</v>
+        <v>0.04486693009301836</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>0.07886018916845154</v>
+        <v>0.07551752174309861</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.05528848097541515</v>
+        <v>0.1079821501300804</v>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
@@ -3700,7 +3708,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Terminal growth reconciliation: actual NOPAT compound growth FY2023–FY2025 was 30.5%; the implied growth from stable years only (FY2024 excluded as a debt-funded capacity burst) is 5.1%; the adopted terminal growth is 5.0%, below the blended nominal ceiling of 10.5%.</t>
+          <t>Terminal growth reconciliation: actual NOPAT compound growth FY2023–FY2025 was 26.9%; the implied growth from stable years only (FY2024 excluded as a debt-funded capacity burst) is 7.6%; the adopted terminal growth is 5.0%, below the blended nominal ceiling of 11.1%.</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3854,7 @@
       </c>
       <c r="C8" s="40" t="inlineStr">
         <is>
-          <t>the right frame for the roughly 27% that is turnkey project work</t>
+          <t>the right frame for the roughly 32% that is the Constructions and infrastructure segment</t>
         </is>
       </c>
       <c r="D8" s="40" t="inlineStr">
@@ -3873,7 +3881,7 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="33">
         <f>'Relative &amp; Normalized'!C13</f>
         <v/>
       </c>
@@ -3884,7 +3892,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="33">
         <f>'Relative &amp; Normalized'!C14</f>
         <v/>
       </c>
@@ -3895,7 +3903,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="B13" s="32">
+      <c r="B13" s="33">
         <f>'Relative &amp; Normalized'!C15</f>
         <v/>
       </c>
@@ -3906,7 +3914,7 @@
           <t>Justified enterprise value / EBITDA applied</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="33">
         <f>'Relative &amp; Normalized'!C6</f>
         <v/>
       </c>
@@ -3917,7 +3925,7 @@
           <t>Justified price / earnings applied</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="33">
         <f>'Relative &amp; Normalized'!C27</f>
         <v/>
       </c>
@@ -4009,14 +4017,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>35.37439268305282</v>
+        <v>19.945090316451</v>
       </c>
       <c r="C5" s="8">
-        <f>DCF!C31</f>
+        <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>110.3869768355961</v>
+        <v>122.3348933382508</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>0.45</v>
@@ -4036,15 +4044,17 @@
           <t>Relative multiples</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>61.2294172643708</v>
+      <c r="B6" s="8">
+        <f>'Relative &amp; Normalized'!C12</f>
+        <v/>
       </c>
       <c r="C6" s="8">
         <f>'Relative &amp; Normalized'!C11</f>
         <v/>
       </c>
-      <c r="D6" s="7" t="n">
-        <v>91.61541724668523</v>
+      <c r="D6" s="8">
+        <f>'Relative &amp; Normalized'!D12</f>
+        <v/>
       </c>
       <c r="E6" s="9" t="n">
         <v>0.2</v>
@@ -4064,15 +4074,17 @@
           <t>Normalised earnings power</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>94.04297714970363</v>
+      <c r="B7" s="8">
+        <f>'Relative &amp; Normalized'!E28</f>
+        <v/>
       </c>
       <c r="C7" s="8">
         <f>'Relative &amp; Normalized'!C28</f>
         <v/>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>154.4991767459417</v>
+      <c r="D7" s="8">
+        <f>'Relative &amp; Normalized'!F28</f>
+        <v/>
       </c>
       <c r="E7" s="9" t="n">
         <v>0.2</v>
@@ -4092,15 +4104,17 @@
           <t>Book value and sustainable return</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>33.76534925901321</v>
+      <c r="B8" s="8">
+        <f>'Relative &amp; Normalized'!E36</f>
+        <v/>
       </c>
       <c r="C8" s="8">
         <f>'Relative &amp; Normalized'!C36</f>
         <v/>
       </c>
-      <c r="D8" s="7" t="n">
-        <v>53.71022096338332</v>
+      <c r="D8" s="8">
+        <f>'Relative &amp; Normalized'!F36</f>
+        <v/>
       </c>
       <c r="E8" s="9" t="n">
         <v>0.15</v>
@@ -4372,7 +4386,7 @@
         </is>
       </c>
       <c r="C5" s="8">
-        <f>DCF!C31</f>
+        <f>DCF!C62</f>
         <v/>
       </c>
     </row>
@@ -4388,7 +4402,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>35.37439268305282</v>
+        <v>19.945090316451</v>
       </c>
     </row>
     <row r="7">
@@ -4403,7 +4417,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>110.3869768355961</v>
+        <v>122.3348933382508</v>
       </c>
     </row>
     <row r="8">
@@ -4480,7 +4494,7 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.600860789848202</v>
+        <v>0.5254856747391311</v>
       </c>
     </row>
     <row r="16">
@@ -4491,7 +4505,7 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>26.9% → 15.1%</t>
+          <t>26.6% → 15.9%</t>
         </is>
       </c>
     </row>
@@ -4501,8 +4515,9 @@
           <t>Hard-currency cost of capital for the foreign leg</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
-        <v>0.10119375</v>
+      <c r="C17" s="22">
+        <f>(1-Assumptions!$C$59)*(Assumptions!$C$56+Assumptions!$C$33*Assumptions!$C$57)+Assumptions!$C$59*Assumptions!$C$58*(1-Assumptions!$C$7)</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -4512,7 +4527,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>91.14622861923802</v>
+        <v>85.97488545126602</v>
       </c>
     </row>
     <row r="19">
@@ -4572,13 +4587,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>137.7034929664235</v>
+        <v>146.6166527148279</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>101.4657316594699</v>
+        <v>107.5464809477679</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>173.941254273377</v>
+        <v>185.6868244818879</v>
       </c>
     </row>
     <row r="24">
@@ -4593,13 +4608,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>66.19078084024615</v>
+        <v>61.91445272087842</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>40.8187533998155</v>
+        <v>37.47247721279566</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>72.60004748131544</v>
+        <v>68.08877752143243</v>
       </c>
     </row>
     <row r="25">
@@ -4614,13 +4629,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>60.72264310179215</v>
+        <v>53.24641887790025</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>49.99375810242254</v>
+        <v>46.17387104421569</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>91.14622861923802</v>
+        <v>85.97488545126602</v>
       </c>
     </row>
     <row r="26">
@@ -4648,7 +4663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4744,7 +4759,7 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <v>2140.777876</v>
       </c>
     </row>
@@ -4755,7 +4770,7 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.25</v>
+        <v>0.245</v>
       </c>
     </row>
     <row r="8">
@@ -4774,14 +4789,14 @@
           <t>FY2025 average USD/EGP</t>
         </is>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="24" t="n">
         <v>49.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Revenue drivers — the unit build</t>
+          <t>Revenue drivers — the three disclosed segments</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
@@ -4798,19 +4813,19 @@
           <t>Copper (USD/tonne)</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="23" t="n">
         <v>13400</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <v>14000</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>14000</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="23" t="n">
         <v>14000</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>14000</v>
       </c>
     </row>
@@ -4820,224 +4835,194 @@
           <t>USD/EGP path</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B13" s="24" t="n">
         <v>51</v>
       </c>
-      <c r="C13" s="23" t="n">
+      <c r="C13" s="24" t="n">
         <v>54</v>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="24" t="n">
         <v>57.5</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="24" t="n">
         <v>61</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="24" t="n">
         <v>64.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Cable volume growth</t>
+          <t>Cables — real (volume) growth over copper x FX</t>
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Cable fabrication uplift over copper</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>1.3</v>
+          <t>Constructions and infrastructure — revenue growth</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Raw-material volume growth</t>
+          <t>Electrical products and digital solutions — revenue growth</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Transformer MVA growth</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Meter unit growth</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0.04</v>
-      </c>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Segment gross margins and corporate cost load</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Order-book conversion rate</t>
+          <t>Cables — gross/segment margin</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>0.265</v>
+        <v>0.145</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>0.255</v>
+        <v>0.153</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>0.25</v>
+        <v>0.155</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Order-book book-to-bill</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="C20" s="24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="D20" s="24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>1</v>
+          <t>Constructions and infrastructure — segment margin</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0.082</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Other-lines revenue growth</t>
+          <t>Electrical products and digital solutions — segment margin</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>0.11</v>
+        <v>0.222</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.1</v>
+        <v>0.224</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>0.09</v>
+        <v>0.226</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>0.08</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Meter price inflation</t>
+          <t>Corporate cost load (% of revenue) — the bridge from segment profit to EBIT</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.08</v>
+        <v>0.0455</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.075</v>
+        <v>0.0465</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0475</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0475</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0485</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Unit gross profit and cost load</t>
+          <t>Capital intensity</t>
         </is>
       </c>
       <c r="B24" s="15" t="n"/>
@@ -5051,466 +5036,450 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Gross profit per unit — growth</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>0.08500000000000001</v>
+          <t>Working capital / revenue</t>
+        </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Non-cable margin recovery factor</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="D26" s="24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E26" s="24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="F26" s="24" t="n">
-        <v>1.1</v>
+          <t>Capital expenditure / revenue</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>0.031</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Operating load (% of revenue)</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n">
-        <v>0.04</v>
+          <t>Depreciation and amortisation / revenue</t>
+        </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Cable gross profit per tonne, FY2025 (EGP)</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="n">
-        <v>88173</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Order book at FY2025 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="n">
-        <v>323700</v>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Cost of capital</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Risk-free rate (10-year local currency)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>0.2231</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Capital intensity</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="15" t="n"/>
-      <c r="D31" s="15" t="n"/>
-      <c r="E31" s="15" t="n"/>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
-      <c r="H31" s="15" t="n"/>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Sovereign default spread (netted out)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>0.034</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Working capital / revenue</t>
+          <t>Equity risk premium</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>0.23</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Capital expenditure / revenue</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>0.024</v>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>1.009</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation / revenue</t>
+          <t>Cost of debt, blended</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>0.0105</v>
+        <v>0.095</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Cost of debt path</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.077</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Cost of capital</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="15" t="n"/>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="15" t="n"/>
-      <c r="H36" s="15" t="n"/>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>0.105</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>Risk-free rate (10-year local currency)</t>
+          <t>Terminal equity risk premium</t>
         </is>
       </c>
       <c r="C37" s="9" t="n">
-        <v>0.2231</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>Sovereign default spread (netted out)</t>
+          <t>Terminal cost of debt</t>
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>0.034</v>
+        <v>0.0888</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
+          <t>Terminal debt weight</t>
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>0.0941</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>Beta</t>
-        </is>
-      </c>
-      <c r="C40" s="25" t="n">
-        <v>1.009</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Cost of debt, blended</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>0.13</v>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Cost of debt path</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="C42" s="9" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>0.106</v>
-      </c>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Balance-sheet and bridge anchors</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
+      <c r="H42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>0.105</v>
+          <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="n">
+        <v>20560.003173</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="n">
-        <v>0.07000000000000001</v>
+          <t>Equity-accounted investees at carrying value (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="n">
+        <v>6757.650507</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="n">
-        <v>0.105</v>
+          <t>Intangible assets and goodwill (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="n">
+        <v>1748.816945</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>0.25</v>
+          <t>FY2025 profit after tax (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="n">
+        <v>19186.550057</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="n">
-        <v>0.05</v>
+          <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="n">
+        <v>17330.24499</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>FY2024 dividend per share (EGP)</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>Balance-sheet and bridge anchors</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="15" t="n"/>
-      <c r="D49" s="15" t="n"/>
-      <c r="E49" s="15" t="n"/>
-      <c r="F49" s="15" t="n"/>
-      <c r="G49" s="15" t="n"/>
-      <c r="H49" s="15" t="n"/>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 dividend per share (EGP, ratified 6 May 2026, paid 4 June 2026)</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>1.85</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>Net bank debt at FY2025 (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C50" s="22" t="n">
-        <v>19789</v>
+          <t>Forecast dividend payout ratio (struck at the actual FY2025 rate)</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Equity-accounted investees at carrying value (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="n">
-        <v>6474</v>
+          <t>Growth in the share of equity-accounted investees</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>Intangible assets and goodwill (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="n">
-        <v>1459.2</v>
+          <t>Yield assumed on surplus cash (blend of EGP deposit and hard-currency rates)</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>FY2025 profit after tax (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C53" s="22" t="n">
-        <v>19180</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 profit after minority interests (EGP mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C54" s="22" t="n">
-        <v>17330</v>
+          <t>Days from the 31-Dec-2025 valuation date to the 5-Aug-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="n">
+        <v>217</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>FY2024 dividend per share (EGP)</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Currency-of-discounting alternative</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="n"/>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="15" t="n"/>
+      <c r="E55" s="15" t="n"/>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>Forecast dividend payout ratio</t>
+          <t>US dollar risk-free rate</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>0.25</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Growth in the share of equity-accounted investees</t>
+          <t>Hard-currency-leg equity risk premium</t>
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>Yield assumed on surplus cash</t>
+          <t>US dollar cost of debt</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>0.1</v>
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Debt weight, USD leg</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="12" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Terminal growth of the USD leg</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>Lens inputs</t>
         </is>
       </c>
-      <c r="B60" s="15" t="n"/>
-      <c r="C60" s="15" t="n"/>
-      <c r="D60" s="15" t="n"/>
-      <c r="E60" s="15" t="n"/>
-      <c r="F60" s="15" t="n"/>
-      <c r="G60" s="15" t="n"/>
-      <c r="H60" s="15" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="C61" s="24" t="n">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="C62" s="24" t="n">
-        <v>9</v>
-      </c>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="15" t="n"/>
+      <c r="D62" s="15" t="n"/>
+      <c r="E62" s="15" t="n"/>
+      <c r="F62" s="15" t="n"/>
+      <c r="G62" s="15" t="n"/>
+      <c r="H62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="n">
-        <v>0.235</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="n">
-        <v>0.45</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
+          <t>Sustainable return on equity</t>
         </is>
       </c>
       <c r="C65" s="9" t="n">
-        <v>0.2</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
+          <t>Weight — discounted cash flow</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
+          <t>Weight — relative</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Weight — normalised</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
           <t>Weight — book</t>
         </is>
       </c>
-      <c r="C67" s="9" t="n">
+      <c r="C69" s="9" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -5599,11 +5568,11 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>C5+C6</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>C7/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5615,7 +5584,7 @@
         </is>
       </c>
       <c r="C8" s="18">
-        <f>-Assumptions!$C$50</f>
+        <f>-Assumptions!$C$43</f>
         <v/>
       </c>
       <c r="D8" s="10">
@@ -5630,7 +5599,7 @@
         </is>
       </c>
       <c r="C9" s="18">
-        <f>Assumptions!$C$51</f>
+        <f>Assumptions!$C$44</f>
         <v/>
       </c>
       <c r="D9" s="10">
@@ -5644,7 +5613,7 @@
           <t>Equity before minority interests</t>
         </is>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>C7+C8+C9</f>
         <v/>
       </c>
@@ -5659,7 +5628,7 @@
           <t>Less minority interests at their share of group profit</t>
         </is>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <f>-C10*$C$15</f>
         <v/>
       </c>
@@ -5675,11 +5644,11 @@
         </is>
       </c>
       <c r="B12" s="15" t="n"/>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>C12/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -5702,7 +5671,7 @@
         </is>
       </c>
       <c r="C15" s="11">
-        <f>(Assumptions!$C$53-Assumptions!$C$54)/Assumptions!$C$53</f>
+        <f>(Assumptions!$C$46-Assumptions!$C$47)/Assumptions!$C$46</f>
         <v/>
       </c>
     </row>
@@ -5717,7 +5686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5771,7 +5740,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Segment margin</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -5803,776 +5772,513 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Cables</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="n">
-        <v>92138.29685490194</v>
+          <t>Cables and its accessories</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>155792.929738</v>
       </c>
       <c r="C5" s="11">
-        <f>B5/$B$12</f>
+        <f>B5/$B$8</f>
         <v/>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.1479665487953016</v>
-      </c>
-      <c r="E5" s="22" t="n">
-        <v>145610.3678770696</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>169133.0260767016</v>
-      </c>
-      <c r="G5" s="22" t="n">
-        <v>187299.1659145696</v>
-      </c>
-      <c r="H5" s="22" t="n">
-        <v>206647.9840977443</v>
-      </c>
-      <c r="I5" s="22" t="n">
-        <v>227245.0290701096</v>
+        <v>0.134899552356732</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>221541.3228857327</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <v>252428.7347156312</v>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>276853.5521024677</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <v>302516.6726712704</v>
+      </c>
+      <c r="I5" s="23" t="n">
+        <v>329470.412277309</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Raw material (copper rod)</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="n">
-        <v>60448.00314509805</v>
+          <t>Constructions and infrastructure</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>90958.55022799999</v>
       </c>
       <c r="C6" s="11">
-        <f>B6/$B$12</f>
+        <f>B6/$B$8</f>
         <v/>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.1239697053155375</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>86793.07467340285</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>99853.94648992721</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>109515.7403864063</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>119667.3733648332</v>
-      </c>
-      <c r="I6" s="22" t="n">
-        <v>130329.5401556179</v>
+        <v>0.06452269254829619</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>107331.08926904</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>122357.4417667056</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>135816.7603610432</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <v>148040.2687935371</v>
+      </c>
+      <c r="I6" s="23" t="n">
+        <v>159883.4902970201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Engineering &amp; construction</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n">
-        <v>87100.7</v>
+          <t>Electrical products and digital solutions</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>34297.601753</v>
       </c>
       <c r="C7" s="11">
-        <f>B7/$B$12</f>
+        <f>B7/$B$8</f>
         <v/>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.08991421158660849</v>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>87399</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>86938.53675000001</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>86428.38797775001</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>85427.48076159229</v>
-      </c>
-      <c r="I7" s="22" t="n">
-        <v>84179.56952301609</v>
+        <v>0.2217300370961013</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>41157.1221036</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>47742.261640176</v>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>53948.75565339887</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>59883.11877527275</v>
+      </c>
+      <c r="I7" s="23" t="n">
+        <v>65871.43065280003</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Transformers</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="n">
-        <v>17703.5</v>
-      </c>
-      <c r="C8" s="11">
-        <f>B8/$B$12</f>
-        <v/>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0.2769882639821222</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>20025.95817760357</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>23704.12363041715</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>26754.93213470232</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>29802.66788222058</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>33088.28987415392</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Meters &amp; digital</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="n">
-        <v>16594.1</v>
-      </c>
-      <c r="C9" s="11">
-        <f>B9/$B$12</f>
-        <v/>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>0.2190169964043364</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>17815.54107615941</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>20109.29198971493</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>22592.78955044473</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>25141.25621173489</v>
-      </c>
-      <c r="I9" s="22" t="n">
-        <v>27977.18991241859</v>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="B8" s="32">
+        <f>SUM(B5:B7)</f>
+        <v/>
+      </c>
+      <c r="C8" s="14">
+        <f>SUM(C5:C7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="32">
+        <f>SUM(E5:E7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="32">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="32">
+        <f>SUM(G5:G7)</f>
+        <v/>
+      </c>
+      <c r="H8" s="32">
+        <f>SUM(H5:H7)</f>
+        <v/>
+      </c>
+      <c r="I8" s="32">
+        <f>SUM(I5:I7)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Other electrical products</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n">
-        <v>3206.5</v>
-      </c>
-      <c r="C10" s="11">
-        <f>B10/$B$12</f>
-        <v/>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>0.4076827342682428</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>3591.28</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>3986.3208</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>4384.952880000001</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>4779.598639200001</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>5161.966530336002</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Segment profit by segment (Note 16 basis)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure investment</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="n">
-        <v>3857.9</v>
-      </c>
-      <c r="C11" s="11">
-        <f>B11/$B$12</f>
-        <v/>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>0.4966473826898447</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>4320.848000000001</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>4796.141280000002</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>5275.755408000002</v>
-      </c>
-      <c r="H11" s="22" t="n">
-        <v>5750.573394720002</v>
-      </c>
-      <c r="I11" s="22" t="n">
-        <v>6210.619266297603</v>
+          <t>Cables and its accessories</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>31015.78520400258</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>36602.16653376652</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>41528.03281537016</v>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>46285.05091870438</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>51067.91390298289</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Total revenue</t>
-        </is>
-      </c>
-      <c r="B12" s="31">
-        <f>SUM(B5:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="14">
-        <f>SUM(C5:C11)</f>
-        <v/>
-      </c>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="31">
-        <f>SUM(E5:E11)</f>
-        <v/>
-      </c>
-      <c r="F12" s="31">
-        <f>SUM(F5:F11)</f>
-        <v/>
-      </c>
-      <c r="G12" s="31">
-        <f>SUM(G5:G11)</f>
-        <v/>
-      </c>
-      <c r="H12" s="31">
-        <f>SUM(H5:H11)</f>
-        <v/>
-      </c>
-      <c r="I12" s="31">
-        <f>SUM(I5:I11)</f>
-        <v/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Constructions and infrastructure</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>7298.51407029472</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>8809.735807202804</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>10322.07378743929</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>11695.18123468943</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>13110.44620435565</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Electrical products and digital solutions</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>9054.566862792</v>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>10598.78208411907</v>
+      </c>
+      <c r="D13" s="23" t="n">
+        <v>12084.52126636135</v>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>13533.58484321164</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>15018.68618883841</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Gross profit by segment</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>FY26E</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>FY27E</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>FY28E</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>FY29E</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>FY30E</t>
-        </is>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Group segment profit</t>
+        </is>
+      </c>
+      <c r="B14" s="32">
+        <f>SUM(B11:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="32">
+        <f>SUM(C11:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="32">
+        <f>SUM(D11:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="32">
+        <f>SUM(E11:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="32">
+        <f>SUM(F11:F13)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Cables</t>
-        </is>
-      </c>
-      <c r="B15" s="22" t="n">
-        <v>25866.09381390937</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>29332.15038497323</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>32793.34413040007</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>36492.43334830921</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>40608.77982999848</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Raw material (copper rod)</t>
-        </is>
-      </c>
-      <c r="B16" s="22" t="n">
-        <v>8455.914930776953</v>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>9497.683650248677</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>10516.31022173785</v>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>11590.02549537728</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>12773.3670984553</v>
+          <t>Group segment-profit margin</t>
+        </is>
+      </c>
+      <c r="B15" s="11">
+        <f>B14/E$8</f>
+        <v/>
+      </c>
+      <c r="C15" s="11">
+        <f>C14/F$8</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>D14/G$8</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>E14/H$8</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
+        <f>F14/I$8</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Engineering &amp; construction</t>
-        </is>
-      </c>
-      <c r="B17" s="22" t="n">
-        <v>7858.412178457996</v>
-      </c>
-      <c r="C17" s="22" t="n">
-        <v>8129.690387904425</v>
-      </c>
-      <c r="D17" s="22" t="n">
-        <v>8315.120189181367</v>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>8372.447592754523</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>8325.833587898298</v>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Segment EBIT contribution — segment profit less the pro-rata corporate load</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Transformers</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="n">
-        <v>5746.110816863308</v>
-      </c>
-      <c r="C18" s="22" t="n">
-        <v>6640.205659967241</v>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>7566.514349532672</v>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>8500.978871699957</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>9550.849762354903</v>
+          <t>Cables and its accessories</t>
+        </is>
+      </c>
+      <c r="B18" s="29">
+        <f>B11-Assumptions!$B$22*E5</f>
+        <v/>
+      </c>
+      <c r="C18" s="29">
+        <f>C11-Assumptions!$C$22*F5</f>
+        <v/>
+      </c>
+      <c r="D18" s="29">
+        <f>D11-Assumptions!$D$22*G5</f>
+        <v/>
+      </c>
+      <c r="E18" s="29">
+        <f>E11-Assumptions!$E$22*H5</f>
+        <v/>
+      </c>
+      <c r="F18" s="29">
+        <f>F11-Assumptions!$F$22*I5</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Meters &amp; digital</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="n">
-        <v>4179.911870032181</v>
-      </c>
-      <c r="C19" s="22" t="n">
-        <v>4740.020060616494</v>
-      </c>
-      <c r="D19" s="22" t="n">
-        <v>5350.297643420868</v>
-      </c>
-      <c r="E19" s="22" t="n">
-        <v>5953.811217598743</v>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>6625.401122943882</v>
+          <t>Constructions and infrastructure</t>
+        </is>
+      </c>
+      <c r="B19" s="29">
+        <f>B12-Assumptions!$B$22*E6</f>
+        <v/>
+      </c>
+      <c r="C19" s="29">
+        <f>C12-Assumptions!$C$22*F6</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>D12-Assumptions!$D$22*G6</f>
+        <v/>
+      </c>
+      <c r="E19" s="29">
+        <f>E12-Assumptions!$E$22*H6</f>
+        <v/>
+      </c>
+      <c r="F19" s="29">
+        <f>F12-Assumptions!$F$22*I6</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Other electrical products</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="n">
-        <v>1464.102849922855</v>
-      </c>
-      <c r="C20" s="22" t="n">
-        <v>1690.160329950944</v>
-      </c>
-      <c r="D20" s="22" t="n">
-        <v>1912.806450338713</v>
-      </c>
-      <c r="E20" s="22" t="n">
-        <v>2123.930227707874</v>
-      </c>
-      <c r="F20" s="22" t="n">
-        <v>2314.889092217389</v>
+          <t>Electrical products and digital solutions</t>
+        </is>
+      </c>
+      <c r="B20" s="29">
+        <f>B13-Assumptions!$B$22*E7</f>
+        <v/>
+      </c>
+      <c r="C20" s="29">
+        <f>C13-Assumptions!$C$22*F7</f>
+        <v/>
+      </c>
+      <c r="D20" s="29">
+        <f>D13-Assumptions!$D$22*G7</f>
+        <v/>
+      </c>
+      <c r="E20" s="29">
+        <f>E13-Assumptions!$E$22*H7</f>
+        <v/>
+      </c>
+      <c r="F20" s="29">
+        <f>F13-Assumptions!$F$22*I7</f>
+        <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure investment</t>
-        </is>
-      </c>
-      <c r="B21" s="22" t="n">
-        <v>2145.937850200651</v>
-      </c>
-      <c r="C21" s="22" t="n">
-        <v>2477.270654271631</v>
-      </c>
-      <c r="D21" s="22" t="n">
-        <v>2803.603423151645</v>
-      </c>
-      <c r="E21" s="22" t="n">
-        <v>3113.047875744363</v>
-      </c>
-      <c r="F21" s="22" t="n">
-        <v>3392.936583838811</v>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Group EBIT</t>
+        </is>
+      </c>
+      <c r="B21" s="32">
+        <f>SUM(B18:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="32">
+        <f>SUM(C18:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="32">
+        <f>SUM(D18:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="32">
+        <f>SUM(E18:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="32">
+        <f>SUM(F18:F20)</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Group gross profit</t>
-        </is>
-      </c>
-      <c r="B22" s="31">
-        <f>SUM(B15:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="31">
-        <f>SUM(C15:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="31">
-        <f>SUM(D15:D21)</f>
-        <v/>
-      </c>
-      <c r="E22" s="31">
-        <f>SUM(E15:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="31">
-        <f>SUM(F15:F21)</f>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Add back depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B22" s="29">
+        <f>Assumptions!$C$27*E8</f>
+        <v/>
+      </c>
+      <c r="C22" s="29">
+        <f>Assumptions!$C$27*F8</f>
+        <v/>
+      </c>
+      <c r="D22" s="29">
+        <f>Assumptions!$C$27*G8</f>
+        <v/>
+      </c>
+      <c r="E22" s="29">
+        <f>Assumptions!$C$27*H8</f>
+        <v/>
+      </c>
+      <c r="F22" s="29">
+        <f>Assumptions!$C$27*I8</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Group gross margin</t>
-        </is>
-      </c>
-      <c r="B23" s="11">
-        <f>B22/E$12</f>
-        <v/>
-      </c>
-      <c r="C23" s="11">
-        <f>C22/F$12</f>
-        <v/>
-      </c>
-      <c r="D23" s="11">
-        <f>D22/G$12</f>
-        <v/>
-      </c>
-      <c r="E23" s="11">
-        <f>E22/H$12</f>
-        <v/>
-      </c>
-      <c r="F23" s="11">
-        <f>F22/I$12</f>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Group EBITDA</t>
+        </is>
+      </c>
+      <c r="B23" s="32">
+        <f>B21+B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="32">
+        <f>C21+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="32">
+        <f>D21+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="32">
+        <f>E21+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="32">
+        <f>F21+F22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Group EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B24" s="11">
+        <f>B23/E$8</f>
+        <v/>
+      </c>
+      <c r="C24" s="11">
+        <f>C23/F$8</f>
+        <v/>
+      </c>
+      <c r="D24" s="11">
+        <f>D23/G$8</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
+        <f>E23/H$8</f>
+        <v/>
+      </c>
+      <c r="F24" s="11">
+        <f>F23/I$8</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Segment EBITDA — gross profit less the operating load</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>FY26E</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>FY27E</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>FY28E</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>FY29E</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>FY30E</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Cables</t>
-        </is>
-      </c>
-      <c r="B26" s="28">
-        <f>B15-Assumptions!$B$27*E5</f>
-        <v/>
-      </c>
-      <c r="C26" s="28">
-        <f>C15-Assumptions!$C$27*F5</f>
-        <v/>
-      </c>
-      <c r="D26" s="28">
-        <f>D15-Assumptions!$D$27*G5</f>
-        <v/>
-      </c>
-      <c r="E26" s="28">
-        <f>E15-Assumptions!$E$27*H5</f>
-        <v/>
-      </c>
-      <c r="F26" s="28">
-        <f>F15-Assumptions!$F$27*I5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Raw material (copper rod)</t>
-        </is>
-      </c>
-      <c r="B27" s="28">
-        <f>B16-Assumptions!$B$27*E6</f>
-        <v/>
-      </c>
-      <c r="C27" s="28">
-        <f>C16-Assumptions!$C$27*F6</f>
-        <v/>
-      </c>
-      <c r="D27" s="28">
-        <f>D16-Assumptions!$D$27*G6</f>
-        <v/>
-      </c>
-      <c r="E27" s="28">
-        <f>E16-Assumptions!$E$27*H6</f>
-        <v/>
-      </c>
-      <c r="F27" s="28">
-        <f>F16-Assumptions!$F$27*I6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Engineering &amp; construction</t>
-        </is>
-      </c>
-      <c r="B28" s="28">
-        <f>B17-Assumptions!$B$27*E7</f>
-        <v/>
-      </c>
-      <c r="C28" s="28">
-        <f>C17-Assumptions!$C$27*F7</f>
-        <v/>
-      </c>
-      <c r="D28" s="28">
-        <f>D17-Assumptions!$D$27*G7</f>
-        <v/>
-      </c>
-      <c r="E28" s="28">
-        <f>E17-Assumptions!$E$27*H7</f>
-        <v/>
-      </c>
-      <c r="F28" s="28">
-        <f>F17-Assumptions!$F$27*I7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Transformers</t>
-        </is>
-      </c>
-      <c r="B29" s="28">
-        <f>B18-Assumptions!$B$27*E8</f>
-        <v/>
-      </c>
-      <c r="C29" s="28">
-        <f>C18-Assumptions!$C$27*F8</f>
-        <v/>
-      </c>
-      <c r="D29" s="28">
-        <f>D18-Assumptions!$D$27*G8</f>
-        <v/>
-      </c>
-      <c r="E29" s="28">
-        <f>E18-Assumptions!$E$27*H8</f>
-        <v/>
-      </c>
-      <c r="F29" s="28">
-        <f>F18-Assumptions!$F$27*I8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Meters &amp; digital</t>
-        </is>
-      </c>
-      <c r="B30" s="28">
-        <f>B19-Assumptions!$B$27*E9</f>
-        <v/>
-      </c>
-      <c r="C30" s="28">
-        <f>C19-Assumptions!$C$27*F9</f>
-        <v/>
-      </c>
-      <c r="D30" s="28">
-        <f>D19-Assumptions!$D$27*G9</f>
-        <v/>
-      </c>
-      <c r="E30" s="28">
-        <f>E19-Assumptions!$E$27*H9</f>
-        <v/>
-      </c>
-      <c r="F30" s="28">
-        <f>F19-Assumptions!$F$27*I9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Other electrical products</t>
-        </is>
-      </c>
-      <c r="B31" s="28">
-        <f>B20-Assumptions!$B$27*E10</f>
-        <v/>
-      </c>
-      <c r="C31" s="28">
-        <f>C20-Assumptions!$C$27*F10</f>
-        <v/>
-      </c>
-      <c r="D31" s="28">
-        <f>D20-Assumptions!$D$27*G10</f>
-        <v/>
-      </c>
-      <c r="E31" s="28">
-        <f>E20-Assumptions!$E$27*H10</f>
-        <v/>
-      </c>
-      <c r="F31" s="28">
-        <f>F20-Assumptions!$F$27*I10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure investment</t>
-        </is>
-      </c>
-      <c r="B32" s="28">
-        <f>B21-Assumptions!$B$27*E11</f>
-        <v/>
-      </c>
-      <c r="C32" s="28">
-        <f>C21-Assumptions!$C$27*F11</f>
-        <v/>
-      </c>
-      <c r="D32" s="28">
-        <f>D21-Assumptions!$D$27*G11</f>
-        <v/>
-      </c>
-      <c r="E32" s="28">
-        <f>E21-Assumptions!$E$27*H11</f>
-        <v/>
-      </c>
-      <c r="F32" s="28">
-        <f>F21-Assumptions!$F$27*I11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Group EBITDA</t>
-        </is>
-      </c>
-      <c r="B33" s="31">
-        <f>SUM(B26:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="31">
-        <f>SUM(C26:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="31">
-        <f>SUM(D26:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="31">
-        <f>SUM(E26:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="31">
-        <f>SUM(F26:F32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Group EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B34" s="11">
-        <f>B33/E$12</f>
-        <v/>
-      </c>
-      <c r="C34" s="11">
-        <f>C33/F$12</f>
-        <v/>
-      </c>
-      <c r="D34" s="11">
-        <f>D33/G$12</f>
-        <v/>
-      </c>
-      <c r="E34" s="11">
-        <f>E33/H$12</f>
-        <v/>
-      </c>
-      <c r="F34" s="11">
-        <f>F33/I$12</f>
-        <v/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>The corporate load is stated on the segment-profit-to-EBIT basis — the same basis as the audited historical bridge — so EBIT falls out first and EBITDA is EBIT plus D&amp;A, not the other way round.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6586,7 +6292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -6636,8 +6342,8 @@
           <t>Justified enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C6" s="32">
-        <f>Assumptions!$C$61</f>
+      <c r="C6" s="33">
+        <f>Assumptions!$C$63</f>
         <v/>
       </c>
     </row>
@@ -6647,7 +6353,7 @@
           <t>Implied enterprise value AS AT end-FY2027 (EGP mn)</t>
         </is>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>C5*C6</f>
         <v/>
       </c>
@@ -6655,10 +6361,10 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Discount factor back to today (year-2)</t>
-        </is>
-      </c>
-      <c r="C8" s="33">
+          <t>Discount factor back to the valuation date (year-2)</t>
+        </is>
+      </c>
+      <c r="C8" s="34">
         <f>DCF!C16</f>
         <v/>
       </c>
@@ -6666,34 +6372,49 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Implied enterprise value TODAY (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C9" s="28">
-        <f>C7*C8</f>
+          <t>Plus present value of the interim FY26-27 free cash flows (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C9" s="18">
+        <f>DCF!B17+DCF!C17</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Less net bank debt, plus associates (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C10" s="28">
-        <f>-Assumptions!$C$50+Assumptions!$C$51</f>
+          <t>Implied enterprise value at 31-Dec-2025 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C10" s="29">
+        <f>C7*C8+C9</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
+          <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
       <c r="B11" s="15" t="n"/>
-      <c r="C11" s="30">
-        <f>(C9+C10)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6</f>
+      <c r="C11" s="31">
+        <f>((C10-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Bear at 5.5× (C) / bull at 8.0× (D), same construction</t>
+        </is>
+      </c>
+      <c r="C12" s="10">
+        <f>((5.5*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D12" s="10">
+        <f>((8.0*C5*C8+C9-Assumptions!$C$43+Assumptions!$C$44)*(1-'SOTP Bridge'!$C$15)/Assumptions!$C$6)*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6703,8 +6424,8 @@
           <t>Trailing enterprise value / EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="34">
-        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$50)/'Income Statement'!D7</f>
+      <c r="C13" s="35">
+        <f>((Assumptions!$C$5*Assumptions!$C$6)+Assumptions!$C$43)/'Income Statement'!D7</f>
         <v/>
       </c>
     </row>
@@ -6714,7 +6435,7 @@
           <t>Trailing price / earnings</t>
         </is>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="35">
         <f>Assumptions!$C$5/'Income Statement'!D18</f>
         <v/>
       </c>
@@ -6725,7 +6446,7 @@
           <t>Trailing price / book</t>
         </is>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>Assumptions!$C$5/C31</f>
         <v/>
       </c>
@@ -6736,15 +6457,15 @@
           <t>Net bank debt / EBITDA</t>
         </is>
       </c>
-      <c r="C16" s="34">
-        <f>Assumptions!$C$50/'Income Statement'!D7</f>
+      <c r="C16" s="35">
+        <f>Assumptions!$C$43/'Income Statement'!D7</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Normalised earnings lens — every component from the same year (FY2028E)</t>
+          <t>Normalised earnings lens — mid-cycle margin (FY2028E) at current (FY2026E) scale</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -6756,18 +6477,18 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle revenue (EGP mn)</t>
+          <t>Current-scale revenue (FY2026E, EGP mn)</t>
         </is>
       </c>
       <c r="C19" s="18">
-        <f>DCF!D5</f>
+        <f>DCF!B5</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA margin</t>
+          <t>Mid-cycle EBITDA margin (FY2028E)</t>
         </is>
       </c>
       <c r="C20" s="16">
@@ -6778,10 +6499,10 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C21" s="28">
+          <t>Normalised EBITDA (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C21" s="29">
         <f>C19*C20</f>
         <v/>
       </c>
@@ -6789,33 +6510,33 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Mid-cycle EBIT (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C22" s="28">
-        <f>C21-C19*Assumptions!$C$34</f>
+          <t>Normalised EBIT (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C22" s="29">
+        <f>C21-C19*Assumptions!$C$27</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Net finance cost (EGP mn)</t>
+          <t>Net finance cost (FY2026E, EGP mn)</t>
         </is>
       </c>
       <c r="C23" s="18">
-        <f>'Income Statement'!G11</f>
+        <f>'Income Statement'!E11</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Share of equity-accounted investees (EGP mn)</t>
+          <t>Share of equity-accounted investees (FY2026E, EGP mn)</t>
         </is>
       </c>
       <c r="C24" s="18">
-        <f>'Income Statement'!G12</f>
+        <f>'Income Statement'!E12</f>
         <v/>
       </c>
     </row>
@@ -6825,7 +6546,7 @@
           <t>Normalised attributable earnings (EGP mn)</t>
         </is>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="29">
         <f>(C22+C23+C24)*(1-Assumptions!$C$7)*(1-'SOTP Bridge'!$C$15)</f>
         <v/>
       </c>
@@ -6847,20 +6568,33 @@
           <t>Justified price / earnings</t>
         </is>
       </c>
-      <c r="C27" s="34">
-        <f>Assumptions!$C$62</f>
+      <c r="C27" s="35">
+        <f>Assumptions!$C$64</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
+          <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
       <c r="B28" s="15" t="n"/>
-      <c r="C28" s="30">
-        <f>C26*C27</f>
+      <c r="C28" s="31">
+        <f>C26*C27*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>bear 7.0× (E) / bull 11.5× (F):</t>
+        </is>
+      </c>
+      <c r="E28" s="10">
+        <f>C26*7*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="F28" s="10">
+        <f>C26*11.5*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6894,7 +6628,7 @@
         </is>
       </c>
       <c r="C32" s="11">
-        <f>Assumptions!$C$63</f>
+        <f>Assumptions!$C$65</f>
         <v/>
       </c>
     </row>
@@ -6912,7 +6646,7 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>Perpetual cost of equity</t>
+          <t>Perpetual (terminal) cost of equity — a steady-state multiple takes a steady-state rate</t>
         </is>
       </c>
       <c r="C34" s="16">
@@ -6926,20 +6660,33 @@
           <t>Justified price / book</t>
         </is>
       </c>
-      <c r="C35" s="34">
-        <f>(C32-Assumptions!$C$47)/(C34-Assumptions!$C$47)</f>
+      <c r="C35" s="35">
+        <f>(C32-Assumptions!$C$40)/(C34-Assumptions!$C$40)</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>Implied value per share (EGP)</t>
+          <t>Implied value per share, rolled to the anchor (EGP)</t>
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
-      <c r="C36" s="30">
-        <f>C31*C35</f>
+      <c r="C36" s="31">
+        <f>C31*C35*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>bear / bull constructions (E / F):</t>
+        </is>
+      </c>
+      <c r="E36" s="10">
+        <f>((Assumptions!$C$65-0.03)/((DCF!C39+DCF!C49)/2-0.03))*C31*DCF!$C$61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>((Assumptions!$C$65+0.02-Assumptions!$C$40)/(DCF!C49-Assumptions!$C$40))*C31*DCF!$C$61-Assumptions!$C$49</f>
         <v/>
       </c>
     </row>
@@ -6954,7 +6701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -7023,23 +6770,23 @@
         </is>
       </c>
       <c r="B5" s="18">
-        <f>Segments!E12</f>
+        <f>Segments!E8</f>
         <v/>
       </c>
       <c r="C5" s="18">
-        <f>Segments!F12</f>
+        <f>Segments!F8</f>
         <v/>
       </c>
       <c r="D5" s="18">
-        <f>Segments!G12</f>
+        <f>Segments!G8</f>
         <v/>
       </c>
       <c r="E5" s="18">
-        <f>Segments!H12</f>
+        <f>Segments!H8</f>
         <v/>
       </c>
       <c r="F5" s="18">
-        <f>Segments!I12</f>
+        <f>Segments!I8</f>
         <v/>
       </c>
     </row>
@@ -7050,23 +6797,23 @@
         </is>
       </c>
       <c r="B6" s="18">
-        <f>Segments!B33</f>
+        <f>Segments!B23</f>
         <v/>
       </c>
       <c r="C6" s="18">
-        <f>Segments!C33</f>
+        <f>Segments!C23</f>
         <v/>
       </c>
       <c r="D6" s="18">
-        <f>Segments!D33</f>
+        <f>Segments!D23</f>
         <v/>
       </c>
       <c r="E6" s="18">
-        <f>Segments!E33</f>
+        <f>Segments!E23</f>
         <v/>
       </c>
       <c r="F6" s="18">
-        <f>Segments!F33</f>
+        <f>Segments!F23</f>
         <v/>
       </c>
     </row>
@@ -7103,24 +6850,24 @@
           <t>Less depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B8" s="28">
-        <f>-B5*Assumptions!$C$34</f>
-        <v/>
-      </c>
-      <c r="C8" s="28">
-        <f>-C5*Assumptions!$C$34</f>
-        <v/>
-      </c>
-      <c r="D8" s="28">
-        <f>-D5*Assumptions!$C$34</f>
-        <v/>
-      </c>
-      <c r="E8" s="28">
-        <f>-E5*Assumptions!$C$34</f>
-        <v/>
-      </c>
-      <c r="F8" s="28">
-        <f>-F5*Assumptions!$C$34</f>
+      <c r="B8" s="29">
+        <f>-B5*Assumptions!$C$27</f>
+        <v/>
+      </c>
+      <c r="C8" s="29">
+        <f>-C5*Assumptions!$C$27</f>
+        <v/>
+      </c>
+      <c r="D8" s="29">
+        <f>-D5*Assumptions!$C$27</f>
+        <v/>
+      </c>
+      <c r="E8" s="29">
+        <f>-E5*Assumptions!$C$27</f>
+        <v/>
+      </c>
+      <c r="F8" s="29">
+        <f>-F5*Assumptions!$C$27</f>
         <v/>
       </c>
     </row>
@@ -7130,23 +6877,23 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>B6+B8</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>C6+C8</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>D6+D8</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>E6+E8</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>F6+F8</f>
         <v/>
       </c>
@@ -7154,26 +6901,26 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>NOPAT — EBIT x (1 - 25%)</t>
-        </is>
-      </c>
-      <c r="B10" s="28">
+          <t>NOPAT — EBIT x (1 - 24%)</t>
+        </is>
+      </c>
+      <c r="B10" s="29">
         <f>B9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>C9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>D9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>E9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>F9*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7184,23 +6931,23 @@
           <t>Add back depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="29">
         <f>-B8</f>
         <v/>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="29">
         <f>-C8</f>
         <v/>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="29">
         <f>-D8</f>
         <v/>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="29">
         <f>-E8</f>
         <v/>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="29">
         <f>-F8</f>
         <v/>
       </c>
@@ -7211,24 +6958,24 @@
           <t>Less capital expenditure</t>
         </is>
       </c>
-      <c r="B12" s="28">
-        <f>-B5*Assumptions!$B$33</f>
-        <v/>
-      </c>
-      <c r="C12" s="28">
-        <f>-C5*Assumptions!$C$33</f>
-        <v/>
-      </c>
-      <c r="D12" s="28">
-        <f>-D5*Assumptions!$D$33</f>
-        <v/>
-      </c>
-      <c r="E12" s="28">
-        <f>-E5*Assumptions!$E$33</f>
-        <v/>
-      </c>
-      <c r="F12" s="28">
-        <f>-F5*Assumptions!$F$33</f>
+      <c r="B12" s="29">
+        <f>-B5*Assumptions!$B$26</f>
+        <v/>
+      </c>
+      <c r="C12" s="29">
+        <f>-C5*Assumptions!$C$26</f>
+        <v/>
+      </c>
+      <c r="D12" s="29">
+        <f>-D5*Assumptions!$D$26</f>
+        <v/>
+      </c>
+      <c r="E12" s="29">
+        <f>-E5*Assumptions!$E$26</f>
+        <v/>
+      </c>
+      <c r="F12" s="29">
+        <f>-F5*Assumptions!$F$26</f>
         <v/>
       </c>
     </row>
@@ -7238,24 +6985,24 @@
           <t>Less change in working capital</t>
         </is>
       </c>
-      <c r="B13" s="28">
-        <f>-(B5-'Income Statement'!D5)*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="C13" s="28">
-        <f>-(C5-B5)*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="D13" s="28">
-        <f>-(D5-C5)*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="E13" s="28">
-        <f>-(E5-D5)*Assumptions!$C$32</f>
-        <v/>
-      </c>
-      <c r="F13" s="28">
-        <f>-(F5-E5)*Assumptions!$C$32</f>
+      <c r="B13" s="29">
+        <f>-(B5*Assumptions!$C$25-'Balance Sheet'!D16)</f>
+        <v/>
+      </c>
+      <c r="C13" s="29">
+        <f>-(C5-B5)*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="D13" s="29">
+        <f>-(D5-C5)*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="E13" s="29">
+        <f>-(E5-D5)*Assumptions!$C$25</f>
+        <v/>
+      </c>
+      <c r="F13" s="29">
+        <f>-(F5-E5)*Assumptions!$C$25</f>
         <v/>
       </c>
     </row>
@@ -7265,23 +7012,23 @@
           <t>Free cash flow to the firm</t>
         </is>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <f>B10+B11+B12+B13</f>
         <v/>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <f>C10+C11+C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>D10+D11+D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>E10+E11+E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>F10+F11+F12+F13</f>
         <v/>
       </c>
@@ -7292,23 +7039,23 @@
           <t>Forward cost of capital</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="36">
         <f>$C$46-($C$46-$C$53)*B57</f>
         <v/>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="36">
         <f>$C$46-($C$46-$C$53)*C57</f>
         <v/>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <f>$C$46-($C$46-$C$53)*D57</f>
         <v/>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="36">
         <f>$C$46-($C$46-$C$53)*E57</f>
         <v/>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="36">
         <f>$C$46-($C$46-$C$53)*F57</f>
         <v/>
       </c>
@@ -7319,23 +7066,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="37">
         <f>1/(1+B15)</f>
         <v/>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="37">
         <f>B16/(1+C15)</f>
         <v/>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="37">
         <f>C16/(1+D15)</f>
         <v/>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="37">
         <f>D16/(1+E15)</f>
         <v/>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="37">
         <f>E16/(1+F15)</f>
         <v/>
       </c>
@@ -7346,23 +7093,23 @@
           <t>Present value of FCFF</t>
         </is>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <f>B14*B16</f>
         <v/>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <f>C14*C16</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <f>D14*D16</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <f>E14*E16</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <f>F14*F16</f>
         <v/>
       </c>
@@ -7370,7 +7117,7 @@
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>TERMINAL VALUE AND BRIDGE</t>
+          <t>TERMINAL VALUE, BRIDGE AND THE ANCHOR ROLL</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7127,7 @@
           <t>Terminal-year NOPAT grown one year (EGP mn)</t>
         </is>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="29">
         <f>F10*(1+C23)</f>
         <v/>
       </c>
@@ -7414,7 +7161,7 @@
         </is>
       </c>
       <c r="C23" s="16">
-        <f>Assumptions!$C$47</f>
+        <f>Assumptions!$C$40</f>
         <v/>
       </c>
     </row>
@@ -7432,10 +7179,10 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Terminal value (EGP mn)</t>
-        </is>
-      </c>
-      <c r="C25" s="28">
+          <t>Terminal value — terminal-year FCFF C20×(1−C22), capitalised (EGP mn)</t>
+        </is>
+      </c>
+      <c r="C25" s="29">
         <f>C20*(1-C22)/(C24-C23)</f>
         <v/>
       </c>
@@ -7446,7 +7193,7 @@
           <t>Present value of the five forecast years (EGP mn)</t>
         </is>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="29">
         <f>SUM(B17:F17)</f>
         <v/>
       </c>
@@ -7457,7 +7204,7 @@
           <t>Present value of the terminal value (EGP mn)</t>
         </is>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="29">
         <f>C25*F16</f>
         <v/>
       </c>
@@ -7479,7 +7226,7 @@
           <t>Enterprise value (EGP mn)</t>
         </is>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="29">
         <f>C26+C27</f>
         <v/>
       </c>
@@ -7498,11 +7245,11 @@
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>Fair value per share (EGP)</t>
+          <t>Fair value per share at 31-Dec-2025 (EGP)</t>
         </is>
       </c>
       <c r="B31" s="15" t="n"/>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <f>C30/Assumptions!$C$6</f>
         <v/>
       </c>
@@ -7521,8 +7268,8 @@
           <t>Risk-free rate, 10-year local currency</t>
         </is>
       </c>
-      <c r="C34" s="37">
-        <f>Assumptions!$C$37</f>
+      <c r="C34" s="22">
+        <f>Assumptions!$C$30</f>
         <v/>
       </c>
     </row>
@@ -7532,8 +7279,8 @@
           <t>Less sovereign default spread (removed to avoid double-counting)</t>
         </is>
       </c>
-      <c r="C35" s="37">
-        <f>Assumptions!$C$38</f>
+      <c r="C35" s="22">
+        <f>Assumptions!$C$31</f>
         <v/>
       </c>
     </row>
@@ -7543,7 +7290,7 @@
           <t>Risk-free rate net of the sovereign spread</t>
         </is>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="36">
         <f>C34-C35</f>
         <v/>
       </c>
@@ -7555,7 +7302,7 @@
         </is>
       </c>
       <c r="C37" s="38">
-        <f>Assumptions!$C$40</f>
+        <f>Assumptions!$C$33</f>
         <v/>
       </c>
     </row>
@@ -7565,8 +7312,8 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C38" s="37">
-        <f>Assumptions!$C$39</f>
+      <c r="C38" s="22">
+        <f>Assumptions!$C$32</f>
         <v/>
       </c>
     </row>
@@ -7576,7 +7323,7 @@
           <t>Cost of equity, explicit window</t>
         </is>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="36">
         <f>C36+C37*C38</f>
         <v/>
       </c>
@@ -7587,8 +7334,8 @@
           <t>Cost of debt, blended</t>
         </is>
       </c>
-      <c r="C40" s="37">
-        <f>Assumptions!$C$41</f>
+      <c r="C40" s="22">
+        <f>Assumptions!$C$34</f>
         <v/>
       </c>
     </row>
@@ -7598,7 +7345,7 @@
           <t>Cost of debt after tax</t>
         </is>
       </c>
-      <c r="C41" s="35">
+      <c r="C41" s="36">
         <f>C40*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7621,7 +7368,7 @@
         </is>
       </c>
       <c r="C43" s="18">
-        <f>Assumptions!$C$50</f>
+        <f>Assumptions!$C$43</f>
         <v/>
       </c>
     </row>
@@ -7631,7 +7378,7 @@
           <t>Debt weight (net debt / (net debt + market capitalisation))</t>
         </is>
       </c>
-      <c r="C44" s="35">
+      <c r="C44" s="36">
         <f>C43/(C43+C42)</f>
         <v/>
       </c>
@@ -7642,7 +7389,7 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C45" s="35">
+      <c r="C45" s="36">
         <f>1-C44</f>
         <v/>
       </c>
@@ -7666,8 +7413,8 @@
           <t>Terminal risk-free rate</t>
         </is>
       </c>
-      <c r="C47" s="37">
-        <f>Assumptions!$C$43</f>
+      <c r="C47" s="22">
+        <f>Assumptions!$C$36</f>
         <v/>
       </c>
     </row>
@@ -7677,8 +7424,8 @@
           <t>Terminal equity risk premium</t>
         </is>
       </c>
-      <c r="C48" s="37">
-        <f>Assumptions!$C$44</f>
+      <c r="C48" s="22">
+        <f>Assumptions!$C$37</f>
         <v/>
       </c>
     </row>
@@ -7688,7 +7435,7 @@
           <t>Terminal cost of equity</t>
         </is>
       </c>
-      <c r="C49" s="35">
+      <c r="C49" s="36">
         <f>C47+C37*C48</f>
         <v/>
       </c>
@@ -7699,8 +7446,8 @@
           <t>Terminal cost of debt</t>
         </is>
       </c>
-      <c r="C50" s="37">
-        <f>Assumptions!$C$45</f>
+      <c r="C50" s="22">
+        <f>Assumptions!$C$38</f>
         <v/>
       </c>
     </row>
@@ -7710,7 +7457,7 @@
           <t>Terminal cost of debt after tax</t>
         </is>
       </c>
-      <c r="C51" s="35">
+      <c r="C51" s="36">
         <f>C50*(1-Assumptions!$C$7)</f>
         <v/>
       </c>
@@ -7721,8 +7468,8 @@
           <t>Terminal debt weight</t>
         </is>
       </c>
-      <c r="C52" s="37">
-        <f>Assumptions!$C$46</f>
+      <c r="C52" s="22">
+        <f>Assumptions!$C$39</f>
         <v/>
       </c>
     </row>
@@ -7777,24 +7524,24 @@
           <t>Cost of debt path</t>
         </is>
       </c>
-      <c r="B56" s="37">
-        <f>Assumptions!$B$42</f>
-        <v/>
-      </c>
-      <c r="C56" s="37">
-        <f>Assumptions!$C$42</f>
-        <v/>
-      </c>
-      <c r="D56" s="37">
-        <f>Assumptions!$D$42</f>
-        <v/>
-      </c>
-      <c r="E56" s="37">
-        <f>Assumptions!$E$42</f>
-        <v/>
-      </c>
-      <c r="F56" s="37">
-        <f>Assumptions!$F$42</f>
+      <c r="B56" s="22">
+        <f>Assumptions!$B$35</f>
+        <v/>
+      </c>
+      <c r="C56" s="22">
+        <f>Assumptions!$C$35</f>
+        <v/>
+      </c>
+      <c r="D56" s="22">
+        <f>Assumptions!$D$35</f>
+        <v/>
+      </c>
+      <c r="E56" s="22">
+        <f>Assumptions!$E$35</f>
+        <v/>
+      </c>
+      <c r="F56" s="22">
+        <f>Assumptions!$F$35</f>
         <v/>
       </c>
     </row>
@@ -7804,23 +7551,23 @@
           <t>Glide fraction — cumulative progress of the easing</t>
         </is>
       </c>
-      <c r="B57" s="35">
+      <c r="B57" s="36">
         <f>($B$56-B56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="C57" s="35">
+      <c r="C57" s="36">
         <f>($B$56-C56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="D57" s="35">
+      <c r="D57" s="36">
         <f>($B$56-D56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="E57" s="35">
+      <c r="E57" s="36">
         <f>($B$56-E56)/($B$56-$F$56)</f>
         <v/>
       </c>
-      <c r="F57" s="35">
+      <c r="F57" s="36">
         <f>($B$56-F56)/($B$56-$F$56)</f>
         <v/>
       </c>
@@ -7829,6 +7576,44 @@
       <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Note: row 15 above is the explicit-window cost of capital walked down to the terminal rate by the glide fraction on row 57, so the shape of the easing is inherited from the cost-of-debt path rather than being a second free parameter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>THE ANCHOR ROLL — one date, one price of time</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Anchor accretion factor — (1 + cost of equity)^(days to anchor / 365)</t>
+        </is>
+      </c>
+      <c r="C61" s="37">
+        <f>(1+C39)^(Assumptions!$C$53/365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>Fair value per share at the 5-Aug-2026 anchor (EGP)</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="31">
+        <f>C31*C61-Assumptions!$C$49</f>
+        <v/>
+      </c>
+      <c r="D62" s="15" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>The bridge on row 31 is dated 31-Dec-2025 (the audited balance-sheet date it subtracts net debt at). Row 62 rolls it to the anchor at the cost of equity, net of the EGP 1.85 FY2025 dividend paid in the window. Every lens on every sheet is rolled the same way.</t>
         </is>
       </c>
     </row>
@@ -7932,32 +7717,32 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
-        <v>152186.2</v>
-      </c>
-      <c r="C5" s="29" t="n">
-        <v>231981.8</v>
-      </c>
-      <c r="D5" s="29" t="n">
-        <v>281049</v>
-      </c>
-      <c r="E5" s="29">
+      <c r="B5" s="30" t="n">
+        <v>152186.247545</v>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>231981.835577</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <v>281049.081719</v>
+      </c>
+      <c r="E5" s="30">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="30">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="30">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="I5" s="29">
+      <c r="I5" s="30">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -7968,33 +7753,33 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
-        <v>29077.3</v>
-      </c>
-      <c r="C6" s="22" t="n">
-        <v>43898.5</v>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>40720</v>
+      <c r="B6" s="23" t="n">
+        <v>29077.288803</v>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>43898.520903</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>40762.108187</v>
       </c>
       <c r="E6" s="18">
-        <f>Segments!B22</f>
+        <f>Segments!B14</f>
         <v/>
       </c>
       <c r="F6" s="18">
-        <f>Segments!C22</f>
+        <f>Segments!C14</f>
         <v/>
       </c>
       <c r="G6" s="18">
-        <f>Segments!D22</f>
+        <f>Segments!D14</f>
         <v/>
       </c>
       <c r="H6" s="18">
-        <f>Segments!E22</f>
+        <f>Segments!E14</f>
         <v/>
       </c>
       <c r="I6" s="18">
-        <f>Segments!F22</f>
+        <f>Segments!F14</f>
         <v/>
       </c>
     </row>
@@ -8004,32 +7789,32 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
-        <v>20035.1</v>
-      </c>
-      <c r="C7" s="29" t="n">
-        <v>31601.6</v>
-      </c>
-      <c r="D7" s="29" t="n">
-        <v>30622.08783333333</v>
-      </c>
-      <c r="E7" s="29">
+      <c r="B7" s="30" t="n">
+        <v>20035.105205</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>31601.46495</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>28363.203246</v>
+      </c>
+      <c r="E7" s="30">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="30">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="30">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -8079,14 +7864,14 @@
           <t>Depreciation and amortisation</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
-        <v>-2296</v>
-      </c>
-      <c r="C9" s="22" t="n">
-        <v>-2259.9</v>
-      </c>
-      <c r="D9" s="22" t="n">
-        <v>-2951.0145</v>
+      <c r="B9" s="23" t="n">
+        <v>-2295.986956</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>-2259.745806</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>-3008.977627</v>
       </c>
       <c r="E9" s="18">
         <f>DCF!B8</f>
@@ -8115,35 +7900,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="30">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="30">
         <f>I7+I9</f>
         <v/>
       </c>
@@ -8154,33 +7939,33 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
-        <v>-2124.4</v>
-      </c>
-      <c r="C11" s="22" t="n">
-        <v>-3515.4</v>
-      </c>
-      <c r="D11" s="22" t="n">
-        <v>-3400</v>
-      </c>
-      <c r="E11" s="28">
-        <f>-(Assumptions!$B$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
-        <v/>
-      </c>
-      <c r="F11" s="28">
-        <f>-(Assumptions!$C$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
-        <v/>
-      </c>
-      <c r="G11" s="28">
-        <f>-(Assumptions!$D$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
-        <v/>
-      </c>
-      <c r="H11" s="28">
-        <f>-(Assumptions!$E$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
-        <v/>
-      </c>
-      <c r="I11" s="28">
-        <f>-(Assumptions!$F$42*'Balance Sheet'!$D$11-Assumptions!$C$58*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
+      <c r="B11" s="23" t="n">
+        <v>-2124.362277</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>-3515.365946</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>-2145.438755</v>
+      </c>
+      <c r="E11" s="29">
+        <f>-(Assumptions!$B$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!D17,0))</f>
+        <v/>
+      </c>
+      <c r="F11" s="29">
+        <f>-(Assumptions!$C$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!E17,0))</f>
+        <v/>
+      </c>
+      <c r="G11" s="29">
+        <f>-(Assumptions!$D$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!F17,0))</f>
+        <v/>
+      </c>
+      <c r="H11" s="29">
+        <f>-(Assumptions!$E$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!G17,0))</f>
+        <v/>
+      </c>
+      <c r="I11" s="29">
+        <f>-(Assumptions!$F$35*'Balance Sheet'!$D$11-Assumptions!$C$52*MAX('Balance Sheet'!$D$11-'Balance Sheet'!H17,0))</f>
         <v/>
       </c>
     </row>
@@ -8190,33 +7975,33 @@
           <t>Share of equity-accounted investees</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
-        <v>603.6</v>
-      </c>
-      <c r="C12" s="22" t="n">
-        <v>1132.4</v>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>1302.26</v>
-      </c>
-      <c r="E12" s="28">
-        <f>D12*(1+Assumptions!$C$57)</f>
-        <v/>
-      </c>
-      <c r="F12" s="28">
-        <f>E12*(1+Assumptions!$C$57)</f>
-        <v/>
-      </c>
-      <c r="G12" s="28">
-        <f>F12*(1+Assumptions!$C$57)</f>
-        <v/>
-      </c>
-      <c r="H12" s="28">
-        <f>G12*(1+Assumptions!$C$57)</f>
-        <v/>
-      </c>
-      <c r="I12" s="28">
-        <f>H12*(1+Assumptions!$C$57)</f>
+      <c r="B12" s="23" t="n">
+        <v>603.624972</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>1132.366257</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>1568.902975</v>
+      </c>
+      <c r="E12" s="29">
+        <f>D12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="F12" s="29">
+        <f>E12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="G12" s="29">
+        <f>F12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="H12" s="29">
+        <f>G12*(1+Assumptions!$C$51)</f>
+        <v/>
+      </c>
+      <c r="I12" s="29">
+        <f>H12*(1+Assumptions!$C$51)</f>
         <v/>
       </c>
     </row>
@@ -8226,35 +8011,35 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="29">
         <f>B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="29">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="29">
         <f>G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="29">
         <f>H10+H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="29">
         <f>I10+I11+I12</f>
         <v/>
       </c>
@@ -8265,32 +8050,32 @@
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B14" s="22" t="n">
-        <v>-5080.4</v>
-      </c>
-      <c r="C14" s="22" t="n">
-        <v>-8121.5</v>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>-6393.333333333332</v>
-      </c>
-      <c r="E14" s="28">
+      <c r="B14" s="23" t="n">
+        <v>-5080.406688</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>-8121.510082</v>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>-5591.139782</v>
+      </c>
+      <c r="E14" s="29">
         <f>-E13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="29">
         <f>-F13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="29">
         <f>-G13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="29">
         <f>-H13*Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="29">
         <f>-I13*Assumptions!$C$7</f>
         <v/>
       </c>
@@ -8301,32 +8086,32 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n">
-        <v>11138</v>
-      </c>
-      <c r="C15" s="22" t="n">
-        <v>18837.2</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>19180</v>
-      </c>
-      <c r="E15" s="28">
+      <c r="B15" s="23" t="n">
+        <v>11137.974256</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>18837.209373</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>19186.550057</v>
+      </c>
+      <c r="E15" s="29">
         <f>E13+E14</f>
         <v/>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="29">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="29">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="29">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="29">
         <f>I13+I14</f>
         <v/>
       </c>
@@ -8337,32 +8122,32 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
-        <v>-1022.299999999999</v>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>-1375.799999999999</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>-1850</v>
-      </c>
-      <c r="E16" s="28">
+      <c r="B16" s="23" t="n">
+        <v>-1022.272478999999</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>-1375.850659</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>-1856.305067000001</v>
+      </c>
+      <c r="E16" s="29">
         <f>-E15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>-F15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>-G15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>-H15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>-I15*'SOTP Bridge'!$C$15</f>
         <v/>
       </c>
@@ -8373,32 +8158,32 @@
           <t>Profit attributable to shareholders</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>10115.7</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>17461.4</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>17330</v>
-      </c>
-      <c r="E17" s="29">
+      <c r="B17" s="30" t="n">
+        <v>10115.701777</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>17461.358714</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>17330.24499</v>
+      </c>
+      <c r="E17" s="30">
         <f>E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="30">
         <f>F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="30">
         <f>G15+G16</f>
         <v/>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="30">
         <f>H15+H16</f>
         <v/>
       </c>
-      <c r="I17" s="29">
+      <c r="I17" s="30">
         <f>I15+I16</f>
         <v/>
       </c>
@@ -8445,7 +8230,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Note: FY2023 and FY2024 are audited. FY2025 revenue, profit after tax and profit after minority interests are disclosed; the intermediate lines are derived by closing the account to the reported profit. In the forecast the finance charge is computed on the gross debt book less the cash the business is accumulating, so it falls with net debt rather than being frozen at the FY2025 balance; profit is therefore struck after interest and differs from the pre-financing DCF waterfall by construction.</t>
+          <t>Note: every FY2023-25 statement line is the audited figure — no closure or derivation is used for any historical year (the EBITDA and EPS rows are labelled house derivations). In the forecast the finance charge is computed on the gross debt book less the cash the business is accumulating, so it moves with net debt rather than being frozen at the FY2025 balance; profit is therefore struck after interest and differs from the pre-financing DCF waterfall by construction.</t>
         </is>
       </c>
     </row>
